--- a/outputs/_eval/bagel-zebra-cot-lora-tagfix-actual/ummmu_table2_bagel-zebra-cot-lora-tagfix-actual.xlsx
+++ b/outputs/_eval/bagel-zebra-cot-lora-tagfix-actual/ummmu_table2_bagel-zebra-cot-lora-tagfix-actual.xlsx
@@ -512,8 +512,17 @@
       <c r="I2">
         <v>7.9</v>
       </c>
+      <c r="J2">
+        <v>52.9</v>
+      </c>
+      <c r="K2">
+        <v>33.1</v>
+      </c>
+      <c r="L2">
+        <v>8.9</v>
+      </c>
       <c r="P2">
-        <v>16.6</v>
+        <v>20.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/_eval/bagel-zebra-cot-lora-tagfix-actual/ummmu_table2_bagel-zebra-cot-lora-tagfix-actual.xlsx
+++ b/outputs/_eval/bagel-zebra-cot-lora-tagfix-actual/ummmu_table2_bagel-zebra-cot-lora-tagfix-actual.xlsx
@@ -521,8 +521,17 @@
       <c r="L2">
         <v>8.9</v>
       </c>
+      <c r="M2">
+        <v>14.5</v>
+      </c>
+      <c r="N2">
+        <v>0.2</v>
+      </c>
+      <c r="O2">
+        <v>0.2</v>
+      </c>
       <c r="P2">
-        <v>20.7</v>
+        <v>17.3</v>
       </c>
     </row>
   </sheetData>
